--- a/input/mapping/050. OCB_GOLD_TCKH_V_ENTRY_STMT_QUYMO_QUANG.xlsx
+++ b/input/mapping/050. OCB_GOLD_TCKH_V_ENTRY_STMT_QUYMO_QUANG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZoneC_BOC\V_CDR_RATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57F63746-6641-4CED-9055-4673C0DB3638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{57F63746-6641-4CED-9055-4673C0DB3638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAA21EC8-5662-4971-88EE-A802DBF4FE38}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>V_ENTRY_STMT_QUYMO  —  Data Lineage Mind Map</t>
   </si>
@@ -133,6 +133,1213 @@
 </t>
   </si>
   <si>
+    <t>code mới</t>
+  </si>
+  <si>
+    <t>ar_dim</t>
+  </si>
+  <si>
+    <t>USE CATALOG IDENTIFIER(:curated);
+USE SCHEMA tckh;
+TRUNCATE TABLE AR_DIM;
+INSERT INTO AR_DIM
+WITH
+-- ── Reference (danh mục gộp) — đọc 1 lần ────────────────────────────────────
+ref_all AS (
+    SELECT ref_hashkey, ref_type, ref_code, ref_description
+    FROM IDENTIFIER(:cleaned || '.raw_vault.reference')
+),
+-- ── STS deleted sets (MAX_BY = 'D'), filter :DATADT ─────────────────────────
+sts_account AS (
+    SELECT account_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_account')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY account_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_loans AS (
+    SELECT loans_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_loans')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_collateral AS (
+    SELECT collateral_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_collateral')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY collateral_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_forex AS (
+    SELECT forex_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_forex')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY forex_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_lc AS (
+    SELECT letter_of_credit_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_letter_of_credit')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY letter_of_credit_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_limit AS (
+    SELECT limit_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_limit')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY limit_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_locked AS (
+    SELECT ac_locked_events_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_account_locked_events')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY ac_locked_events_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_drawings AS (
+    SELECT drawings_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_drawings')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY drawings_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_repo AS (
+    SELECT repo_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_repo')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY repo_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_sec_trade AS (
+    SELECT sec_trade_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_sec_trade')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY sec_trade_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_sc_trading AS (
+    SELECT sc_trading_position_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_sc_trading_position')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY sc_trading_position_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_md_deal AS (
+    SELECT md_deal_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_md_deal')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY md_deal_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_money_market AS (
+    SELECT money_market_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_money_market')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY money_market_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+sts_payment_due AS (
+    SELECT loans_payment_due_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_loans_payment_due')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_payment_due_hashkey
+    HAVING MAX_BY(cdc_status, source_event_date) = 'D'
+),
+-- ── Satellite _information (name / status) ──────────────────────────────────
+sat_account AS (
+    SELECT account_hashkey,
+        MAX_BY(t_short_title,   source_event_date) AS ar_nm,
+        MAX_BY(t_record_status, source_event_date) AS ar_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_information')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY account_hashkey
+),
+sat_loans AS (
+    SELECT loans_hashkey,
+        MAX_BY(t_status, source_event_date) AS ar_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_loans_information')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+),
+sat_collateral AS (
+    SELECT ci.collateral_hashkey, ci.ar_status,
+           r.ref_hashkey AS ar_tp_id, r.ref_description AS ar_tp_nm
+    FROM (
+        SELECT collateral_hashkey,
+            MAX_BY(t_coll_status,     source_event_date) AS ar_status,
+            MAX_BY(t_collateral_type, source_event_date) AS coll_type
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_collateral_information')
+        WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+        GROUP BY collateral_hashkey
+    ) ci
+    LEFT JOIN ref_all r ON r.ref_type = 'COLLATERAL_TYPE' AND r.ref_code = ci.coll_type
+),
+sat_md_deal AS (
+    SELECT mi.md_deal_hashkey, mi.ar_status,
+           r.ref_hashkey AS ar_tp_id, r.ref_description AS ar_tp_nm
+    FROM (
+        SELECT md_deal_hashkey,
+            MAX_BY(t_status,   source_event_date) AS ar_status,
+            MAX_BY(t_category, source_event_date) AS cat
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_md_deal_information')
+        WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+        GROUP BY md_deal_hashkey
+    ) mi
+    LEFT JOIN ref_all r ON r.ref_type = 'CATEGORY' AND r.ref_code = mi.cat
+),
+sat_payment_due AS (
+    SELECT loans_payment_due_hashkey,
+        MAX_BY(t_status, source_event_date) AS ar_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_loans_payment_due_information')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_payment_due_hashkey
+),
+-- ── Satellite _classification -&gt; AR_TP_ID (ref_hashkey) + AR_TP_NM ──────────
+sat_account_cls AS (
+    SELECT a.account_hashkey, r.ref_hashkey AS ar_tp_id, r.ref_description AS ar_tp_nm
+    FROM (
+        SELECT account_hashkey, MAX_BY(t_category, source_event_date) AS cat
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_classification')
+        WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+        GROUP BY account_hashkey
+    ) a
+    LEFT JOIN ref_all r ON r.ref_type = 'CATEGORY' AND r.ref_code = a.cat
+),
+sat_loans_cls AS (
+    SELECT a.loans_hashkey, r.ref_hashkey AS ar_tp_id, r.ref_description AS ar_tp_nm
+    FROM (
+        SELECT loans_hashkey, MAX_BY(t_category, source_event_date) AS cat
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_loans_classification')
+        WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+        GROUP BY loans_hashkey
+    ) a
+    LEFT JOIN ref_all r ON r.ref_type = 'CATEGORY' AND r.ref_code = a.cat
+),
+sat_forex_cls AS (
+    SELECT a.forex_hashkey, r.ref_hashkey AS ar_tp_id, r.ref_description AS ar_tp_nm
+    FROM (
+        SELECT forex_hashkey, MAX_BY(t_category, source_event_date) AS cat
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_forex_classification')
+        WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+        GROUP BY forex_hashkey
+    ) a
+    LEFT JOIN ref_all r ON r.ref_type = 'CATEGORY' AND r.ref_code = a.cat
+),
+sat_lc_cls AS (
+    -- t_category_code -&gt; ref_type='LC_TYPES' (fix từ 'CATEGORY')
+    SELECT a.letter_of_credit_hashkey, r.ref_hashkey AS ar_tp_id, r.ref_description AS ar_tp_nm
+    FROM (
+        SELECT letter_of_credit_hashkey, MAX_BY(t_category_code, source_event_date) AS cat
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_classification')
+        WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+        GROUP BY letter_of_credit_hashkey
+    ) a
+    LEFT JOIN ref_all r ON r.ref_type = 'LC_TYPES' AND r.ref_code = a.cat
+),
+sat_mm_cls AS (
+    SELECT a.money_market_hashkey, r.ref_hashkey AS ar_tp_id, r.ref_description AS ar_tp_nm
+    FROM (
+        SELECT money_market_hashkey, MAX_BY(t_category, source_event_date) AS cat
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_money_market_classification')
+        WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+        GROUP BY money_market_hashkey
+    ) a
+    LEFT JOIN ref_all r ON r.ref_type = 'CATEGORY' AND r.ref_code = a.cat
+),
+sat_repo_cls AS (
+    SELECT repo_hashkey,
+        MAX_BY(product_category, source_event_date) AS ar_tp_id
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_repo_classification')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY repo_hashkey
+),
+sat_drawings AS (
+    SELECT drawings_hashkey,
+        MAX_BY(t_drawing_type, source_event_date) AS ar_tp_id
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_drawings_information')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY drawings_hashkey
+),
+sat_passbook AS (
+    SELECT passbook_hashkey,
+        MAX_BY(passbooktype, source_event_date) AS ar_tp_id
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_passbook')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY passbook_hashkey
+),
+-- ── Satellite status ở _audit_status / _system ──────────────────────────────
+sat_forex_st AS (
+    SELECT forex_hashkey, MAX_BY(t_status, source_event_date) AS ar_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_forex_audit_status')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY forex_hashkey
+),
+sat_mm_st AS (
+    SELECT money_market_hashkey, MAX_BY(t_status, source_event_date) AS ar_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_money_market_audit_status')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY money_market_hashkey
+),
+sat_lc_st AS (
+    SELECT letter_of_credit_hashkey, MAX_BY(t_record_status, source_event_date) AS ar_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_system')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY letter_of_credit_hashkey
+),
+-- ── Snapshot hub_account 1 lần — dùng cho account + az_account ──────────────
+hub_account_snap AS (
+    SELECT account_hashkey, business_key, record_source, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account')
+    WHERE record_source IN ('t24__t24_account', 't24__t24_az_account')
+),
+cte_all AS (
+    -- ── Block 1+14 — T24_ACCOUNT + T24_AZ_ACCOUNT (gộp)
+    SELECT h.account_hashkey AS AR_DW_ID, h.business_key AS AR_DIM_ID,
+           s.ar_nm AS AR_NM, c.ar_tp_id AS AR_TP_ID, c.ar_tp_nm AS AR_TP_NM,
+           s.ar_status AS AR_LC_ST_TP, h.source_event_date AS source_event_date
+    FROM hub_account_snap h
+    LEFT JOIN sts_account     d ON h.account_hashkey = d.account_hashkey
+    LEFT JOIN sat_account     s ON h.account_hashkey = s.account_hashkey
+    LEFT JOIN sat_account_cls c ON h.account_hashkey = c.account_hashkey
+    WHERE d.account_hashkey IS NULL
+    UNION ALL
+    -- ── Block 2 — T24_LOANS_AND_DEPOSITS
+    SELECT h.loans_hashkey, h.business_key, CAST(NULL AS STRING), c.ar_tp_id, c.ar_tp_nm,
+           s.ar_status, h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_loans') h
+    LEFT JOIN sts_loans     d ON h.loans_hashkey = d.loans_hashkey
+    LEFT JOIN sat_loans     s ON h.loans_hashkey = s.loans_hashkey
+    LEFT JOIN sat_loans_cls c ON h.loans_hashkey = c.loans_hashkey
+    WHERE h.record_source = 't24__t24_loans_and_deposits' AND d.loans_hashkey IS NULL
+    UNION ALL
+    -- ── Block 3 — T24_COLLATERAL
+    SELECT h.collateral_hashkey, h.business_key, CAST(NULL AS STRING), s.ar_tp_id, s.ar_tp_nm,
+           s.ar_status, h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_collateral') h
+    LEFT JOIN sts_collateral d ON h.collateral_hashkey = d.collateral_hashkey
+    LEFT JOIN sat_collateral s ON h.collateral_hashkey = s.collateral_hashkey
+    WHERE h.record_source = 't24__t24_collateral' AND d.collateral_hashkey IS NULL
+    UNION ALL
+    -- ── Block 4 — T24_FOREX
+    SELECT h.forex_hashkey, h.business_key, CAST(NULL AS STRING), c.ar_tp_id, c.ar_tp_nm,
+           st.ar_status, h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_forex') h
+    LEFT JOIN sts_forex     d  ON h.forex_hashkey = d.forex_hashkey
+    LEFT JOIN sat_forex_cls c  ON h.forex_hashkey = c.forex_hashkey
+    LEFT JOIN sat_forex_st  st ON h.forex_hashkey = st.forex_hashkey
+    WHERE h.record_source = 't24__t24_forex' AND d.forex_hashkey IS NULL
+    UNION ALL
+    -- ── Block 5 — T24_LETTER_OF_CREDIT
+    SELECT h.letter_of_credit_hashkey, h.business_key, CAST(NULL AS STRING), c.ar_tp_id, c.ar_tp_nm,
+           st.ar_status, h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_letter_of_credit') h
+    LEFT JOIN sts_lc     d  ON h.letter_of_credit_hashkey = d.letter_of_credit_hashkey
+    LEFT JOIN sat_lc_cls c  ON h.letter_of_credit_hashkey = c.letter_of_credit_hashkey
+    LEFT JOIN sat_lc_st  st ON h.letter_of_credit_hashkey = st.letter_of_credit_hashkey
+    WHERE h.record_source = 't24__t24_letter_of_credit' AND d.letter_of_credit_hashkey IS NULL
+    UNION ALL
+    -- ── Block 6 — T24_LIMIT
+    SELECT h.limit_hashkey, h.business_key, CAST(NULL AS STRING), CAST(NULL AS STRING), CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_limit') h
+    LEFT JOIN sts_limit d ON h.limit_hashkey = d.limit_hashkey
+    WHERE h.record_source = 't24__t24_limit' AND d.limit_hashkey IS NULL
+    UNION ALL
+    -- ── Block 7 — COMB_CONSUMER_LOAN (không có sts_hub_consumer_loan)
+    SELECT h.consumer_loan_hashkey, h.business_key, CAST(NULL AS STRING), CAST(NULL AS STRING), CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_consumer_loan') h
+    WHERE h.record_source = 't24__comb_consumer_loan'
+    UNION ALL
+    -- ── Block 8 — PASSBOOKMAN_PASSBOOK
+    SELECT h.passbook_hashkey, h.business_key, CAST(NULL AS STRING), s.ar_tp_id, CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_passbook') h
+    LEFT JOIN sat_passbook s ON h.passbook_hashkey = s.passbook_hashkey
+    WHERE h.record_source = 't24__passbookman_passbook'
+    UNION ALL
+    -- ── Block 9 — T24_AC_LOCKED_EVENTS
+    SELECT h.ac_locked_events_hashkey, h.business_key, CAST(NULL AS STRING), CAST(NULL AS STRING), CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account_locked_events') h
+    LEFT JOIN sts_locked d ON h.ac_locked_events_hashkey = d.ac_locked_events_hashkey
+    WHERE h.record_source = 't24__t24_ac_locked_events' AND d.ac_locked_events_hashkey IS NULL
+    UNION ALL
+    -- ── Block 10 — T24_DRAWINGS (AR_TP_ID = mã thô; status NULL)
+    SELECT h.drawings_hashkey, h.business_key, CAST(NULL AS STRING), s.ar_tp_id, CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_drawings') h
+    LEFT JOIN sts_drawings d ON h.drawings_hashkey = d.drawings_hashkey
+    LEFT JOIN sat_drawings s ON h.drawings_hashkey = s.drawings_hashkey
+    WHERE h.record_source = 't24__t24_drawings' AND d.drawings_hashkey IS NULL
+    UNION ALL
+    -- ── Block 11 — T24_REPO (AR_TP_ID = mã thô; status NULL)
+    SELECT h.repo_hashkey, h.business_key, CAST(NULL AS STRING), c.ar_tp_id, CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_repo') h
+    LEFT JOIN sts_repo     d ON h.repo_hashkey = d.repo_hashkey
+    LEFT JOIN sat_repo_cls c ON h.repo_hashkey = c.repo_hashkey
+    WHERE h.record_source = 't24__t24_repo' AND d.repo_hashkey IS NULL
+    UNION ALL
+    -- ── Block 12 — T24_SC_TRADING_POSITION
+    SELECT h.sc_trading_position_hashkey, h.business_key, CAST(NULL AS STRING), CAST(NULL AS STRING), CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_sc_trading_position') h
+    LEFT JOIN sts_sc_trading d ON h.sc_trading_position_hashkey = d.sc_trading_position_hashkey
+    WHERE h.record_source = 't24__t24_sc_trading_position' AND d.sc_trading_position_hashkey IS NULL
+    UNION ALL
+    -- ── Block 13 — T24_SEC_TRADE
+    SELECT h.sec_trade_hashkey, h.business_key, CAST(NULL AS STRING), CAST(NULL AS STRING), CAST(NULL AS STRING),
+           CAST(NULL AS STRING), h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_sec_trade') h
+    LEFT JOIN sts_sec_trade d ON h.sec_trade_hashkey = d.sec_trade_hashkey
+    WHERE h.record_source = 't24__t24_sec_trade' AND d.sec_trade_hashkey IS NULL
+    UNION ALL
+    -- ── Block 15 — T24_MD_DEAL
+    SELECT h.md_deal_hashkey, h.business_key, CAST(NULL AS STRING), s.ar_tp_id, s.ar_tp_nm,
+           s.ar_status, h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_md_deal') h
+    LEFT JOIN sts_md_deal d ON h.md_deal_hashkey = d.md_deal_hashkey
+    LEFT JOIN sat_md_deal s ON h.md_deal_hashkey = s.md_deal_hashkey
+    WHERE h.record_source = 't24__t24_md_deal' AND d.md_deal_hashkey IS NULL
+    UNION ALL
+    -- ── Block 16 — T24_MONEY_MARKET
+    SELECT h.money_market_hashkey, h.business_key, CAST(NULL AS STRING), c.ar_tp_id, c.ar_tp_nm,
+           st.ar_status, h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_money_market') h
+    LEFT JOIN sts_money_market d  ON h.money_market_hashkey = d.money_market_hashkey
+    LEFT JOIN sat_mm_cls       c  ON h.money_market_hashkey = c.money_market_hashkey
+    LEFT JOIN sat_mm_st        st ON h.money_market_hashkey = st.money_market_hashkey
+    WHERE h.record_source = 't24__t24_money_market' AND d.money_market_hashkey IS NULL
+    UNION ALL
+    -- ── Block 17 — T24_PAYMENT_DUE
+    SELECT h.loans_payment_due_hashkey, h.business_key, CAST(NULL AS STRING), CAST(NULL AS STRING), CAST(NULL AS STRING),
+           s.ar_status, h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_loans_payment_due') h
+    LEFT JOIN sts_payment_due d ON h.loans_payment_due_hashkey = d.loans_payment_due_hashkey
+    LEFT JOIN sat_payment_due s ON h.loans_payment_due_hashkey = s.loans_payment_due_hashkey
+    WHERE h.record_source = 't24__t24_payment_due' AND d.loans_payment_due_hashkey IS NULL
+),
+-- ── Dedup theo AR_DW_ID bằng MAX_BY ─────────────────────────────────────────
+cte_dedup AS (
+    SELECT
+        AR_DW_ID,
+        MAX_BY(AR_DIM_ID,   source_event_date) AS AR_DIM_ID,
+        MAX_BY(AR_NM,       source_event_date) AS AR_NM,
+        MAX_BY(AR_TP_ID,    source_event_date) AS AR_TP_ID,
+        MAX_BY(AR_TP_NM,    source_event_date) AS AR_TP_NM,
+        MAX_BY(AR_LC_ST_TP, source_event_date) AS AR_LC_ST_TP
+    FROM cte_all
+    GROUP BY AR_DW_ID
+)
+SELECT
+    AR_DW_ID,
+    AR_DIM_ID,
+    AR_DIM_ID           AS AR_ID,
+    AR_NM,
+    AR_TP_ID,
+    AR_TP_ID            AS AR_TP,
+    AR_LC_ST_TP,
+    NULL                AS AR_TERM_TP,
+    AR_TP_NM,
+    CURRENT_TIMESTAMP() AS PPN_TM
+FROM cte_dedup</t>
+  </si>
+  <si>
+    <t>pst_entr_fct</t>
+  </si>
+  <si>
+    <t>USE CATALOG IDENTIFIER(:curated);
+USE SCHEMA tckh;
+DELETE FROM pst_entr_fct
+WHERE  CDR_DT_ID = CAST(:DATADT AS INT);
+INSERT INTO pst_entr_fct
+    (PST_ENTR_ID, AMT_FCY, AMT_LCY, NBR_OF_ITM, CCY_ID, CST_ID, AR_ID, LINE_NBR, TXN_TP_ID, CGY_ID,
+     PST_ENTR_ST_ID, INPUTER_ID, APRV_ID, CDR_DT_ID, OU_ID, OU_DW_ID, INPTR_DW_ID, APRV_DW_ID,
+     OU_ID_CREATED, AUTO_DIM_ID, CRT_TM, PPN_TM, GL_CDR_DT_ID, INPTR_DW_ID_COM, OU_ID_CREATED_COM)
+WITH
+user_sts_del AS (
+    SELECT user_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_user')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY user_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+user_active AS (
+    SELECT h.user_hashkey, h.business_key
+    FROM      IDENTIFIER(:cleaned || '.raw_vault.hub_user') h
+    LEFT JOIN user_sts_del x ON x.user_hashkey = h.user_hashkey
+    WHERE  x.user_hashkey IS NULL
+      AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY h.user_hashkey, h.business_key
+),
+branch_sts_del AS (
+    SELECT branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY branch_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+branch_hub AS (
+    SELECT branch_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY branch_hashkey, business_key
+),
+branch_active AS (
+    SELECT h.branch_hashkey, h.business_key
+    FROM      branch_hub h
+    LEFT JOIN branch_sts_del x ON x.branch_hashkey = h.branch_hashkey
+    WHERE  x.branch_hashkey IS NULL
+),
+account_sts_del AS (
+    SELECT account_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_account')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY account_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+account_hub AS (
+    SELECT account_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_account')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY account_hashkey, business_key
+),
+account_active AS (
+    SELECT h.account_hashkey AS ar_dw_id, h.business_key   -- alias khác tên khoá join (X.5)
+    FROM      account_hub h
+    LEFT JOIN account_sts_del x ON x.account_hashkey = h.account_hashkey
+    WHERE  x.account_hashkey IS NULL
+),
+loans_sts_del AS (
+    SELECT loans_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_loans')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+loans_hub AS (
+    SELECT loans_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_loans')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey, business_key
+),
+loans_active AS (
+    SELECT h.loans_hashkey, h.business_key
+    FROM      loans_hub h
+    LEFT JOIN loans_sts_del x ON x.loans_hashkey = h.loans_hashkey
+    WHERE  x.loans_hashkey IS NULL
+),
+forex_sts_del AS (
+    SELECT forex_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_forex')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY forex_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+forex_active AS (
+    SELECT h.forex_hashkey, h.business_key
+    FROM      IDENTIFIER(:cleaned || '.raw_vault.hub_forex') h
+    LEFT JOIN forex_sts_del x ON x.forex_hashkey = h.forex_hashkey
+    WHERE  x.forex_hashkey IS NULL
+      AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY h.forex_hashkey, h.business_key
+),
+money_market_sts_del AS (
+    SELECT money_market_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_money_market')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY money_market_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+money_market_active AS (
+    SELECT h.money_market_hashkey, h.business_key
+    FROM      IDENTIFIER(:cleaned || '.raw_vault.hub_money_market') h
+    LEFT JOIN money_market_sts_del x ON x.money_market_hashkey = h.money_market_hashkey
+    WHERE  x.money_market_hashkey IS NULL
+      AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY h.money_market_hashkey, h.business_key
+),
+letter_of_credit_sts_del AS (
+    SELECT letter_of_credit_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_letter_of_credit')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY letter_of_credit_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+letter_of_credit_active AS (
+    SELECT h.letter_of_credit_hashkey, h.business_key
+    FROM      IDENTIFIER(:cleaned || '.raw_vault.hub_letter_of_credit') h
+    LEFT JOIN letter_of_credit_sts_del x ON x.letter_of_credit_hashkey = h.letter_of_credit_hashkey
+    WHERE  x.letter_of_credit_hashkey IS NULL
+      AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY h.letter_of_credit_hashkey, h.business_key
+),
+deposits_sts_del AS (
+    SELECT deposit_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_deposits')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY deposit_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+deposits_active AS (
+    SELECT h.deposit_hashkey, h.business_key
+    FROM      IDENTIFIER(:cleaned || '.raw_vault.hub_deposits') h
+    LEFT JOIN deposits_sts_del x ON x.deposit_hashkey = h.deposit_hashkey
+    WHERE  x.deposit_hashkey IS NULL
+      AND h.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY h.deposit_hashkey, h.business_key
+),
+-- satellite snapshot: lay ban ghi moi nhat tinh den ngay chay
+sat_usr_info AS (
+    SELECT user_hashkey,
+           max_by(t_sign_on_name, source_event_date) AS t_sign_on_name
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_user_information')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY user_hashkey
+),
+sat_usr_other AS (
+    SELECT user_hashkey,
+           max_by(t_comp_report,    source_event_date) AS t_comp_report,
+           max_by(t_ocb_department, source_event_date) AS t_ocb_department
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_user_other')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY user_hashkey
+),
+sat_ft_sys AS (
+    SELECT funds_transfer_hashkey,
+           max_by(t_user_input, source_event_date) AS t_user_input,
+           max_by(t_inputter,   source_event_date) AS t_inputter,
+           max_by(t_user_auth,  source_event_date) AS t_user_auth,
+           max_by(t_authoriser, source_event_date) AS t_authoriser
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_funds_transfer_system')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY funds_transfer_hashkey
+),
+sat_tlr_other AS (
+    SELECT teller_hashkey,
+           max_by(t_inputter,   source_event_date) AS t_inputter,
+           max_by(t_authoriser, source_event_date) AS t_authoriser
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_teller_other')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY teller_hashkey
+),
+sat_soa_ft_info AS (
+    SELECT soa_cust_ft_hashkey,
+           max_by(channel, source_event_date) AS channel
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_soa_cust_ft_information')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY soa_cust_ft_hashkey
+),
+sat_hdtg_dn AS (
+    SELECT serial_no,
+           max_by(account_no, source_event_date) AS account_no
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_soa_hdtg_da_nang_information')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY serial_no
+),
+sat_td_detail AS (
+    SELECT hdtg_dn_id,
+           max_by(soa_cust_termdeposit_hashkey, source_event_date) AS soa_cust_termdeposit_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_soa_cust_termdeposit_detail')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY hdtg_dn_id
+),
+sat_td_info AS (
+    SELECT soa_cust_termdeposit_hashkey,
+           max_by(user_created, source_event_date) AS user_created
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_soa_cust_termdeposit_information')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY soa_cust_termdeposit_hashkey
+),
+sat_fx_info AS (
+    SELECT forex_hashkey,
+           max_by(t_deal_date,       source_event_date) AS t_deal_date,
+           max_by(t_value_date_buy,  source_event_date) AS t_value_date_buy,
+           max_by(t_value_date_sell, source_event_date) AS t_value_date_sell
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_forex_information')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY forex_hashkey
+),
+sat_mm_info AS (
+    SELECT money_market_hashkey,
+           max_by(t_maturity_date, source_event_date) AS t_maturity_date
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_money_market_information')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY money_market_hashkey
+),
+lnk_ft_branch AS (
+    SELECT funds_transfer_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_funds_transfer_branch')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY funds_transfer_hashkey
+),
+lnk_tlr_branch AS (
+    SELECT teller_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_teller_branch')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY teller_hashkey
+),
+lnk_tlr_cust AS (
+    SELECT teller_hashkey,
+           max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_teller_customer1')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY teller_hashkey
+),
+lnk_loans_branch AS (
+    SELECT loans_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_loans_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+),
+usr AS (
+    SELECT hu.user_hashkey, hu.business_key AS usr_id, ui.t_sign_on_name,
+           uo.t_comp_report, uo.t_ocb_department,
+           CASE WHEN hu.business_key LIKE '%COB%'     OR hu.business_key LIKE '%ATM%'
+                  OR hu.business_key LIKE '%OSB%'     OR hu.business_key LIKE '%VANHANH%'
+                  OR hu.business_key LIKE '%XULY%'    OR hu.business_key LIKE '%BOSC%'
+                  OR hu.business_key LIKE '%CASHMNG%' OR hu.business_key LIKE '%SWIFTUSER%'
+                  OR hu.business_key LIKE '%CITAD%'   OR hu.business_key LIKE '%DMUSER%'
+                  OR hu.business_key LIKE '%ESB%'     OR hu.business_key LIKE '%OFS%'
+                THEN 1 ELSE 0 END AS auto_user,
+           CASE WHEN uo.t_ocb_department = 'PROJECT DVTD'
+                 AND hu.business_key NOT LIKE 'COB%' THEN 1 ELSE 0 END AS user_com
+    FROM   user_active hu
+           LEFT JOIN sat_usr_info  ui ON ui.user_hashkey = hu.user_hashkey
+           LEFT JOIN sat_usr_other uo ON uo.user_hashkey = hu.user_hashkey
+),
+txn AS (
+    SELECT SPLIT_PART(h.business_key,';',1)         AS txn_ref,
+           h.funds_transfer_hashkey                 AS ft_hashkey,
+           COALESCE(s.t_user_input, s.t_inputter)   AS dvc_id,
+           COALESCE(s.t_user_auth , s.t_authoriser) AS txn_aprv,
+           lb.branch_hashkey                        AS txn_ou_ip_id,
+           CAST(NULL AS STRING)                     AS txn_cst
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_funds_transfer') h
+           LEFT JOIN sat_ft_sys s  ON s.funds_transfer_hashkey  = h.funds_transfer_hashkey
+           LEFT JOIN lnk_ft_branch lb ON lb.funds_transfer_hashkey = h.funds_transfer_hashkey
+    WHERE  h.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    UNION ALL
+    SELECT SPLIT_PART(h.business_key,';',1), CAST(NULL AS STRING),
+           NULLIF(SPLIT_PART(o.t_inputter  ,'_',2),''),
+           NULLIF(SPLIT_PART(o.t_authoriser,'_',2),''),
+           lb.branch_hashkey, lc.customer_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_teller') h
+           LEFT JOIN sat_tlr_other o  ON o.teller_hashkey  = h.teller_hashkey
+           LEFT JOIN lnk_tlr_branch lb ON lb.teller_hashkey = h.teller_hashkey
+           LEFT JOIN lnk_tlr_cust   lc ON lc.teller_hashkey = h.teller_hashkey
+    WHERE  h.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+lnk_soa_ft AS (
+    SELECT funds_transfer_hashkey,
+           max_by(soa_cust_ft_hashkey, source_event_date) AS soa_cust_ft_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_soa_cust_ft_funds_transfer')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY funds_transfer_hashkey
+),
+chan AS (
+    SELECT lsf.funds_transfer_hashkey AS ft_hashkey,
+           CASE WHEN UPPER(sfi.channel) = 'TELLER' THEN 'BRANCH' ELSE sfi.channel END AS channel_code
+    FROM   lnk_soa_ft lsf
+           LEFT JOIN sat_soa_ft_info sfi ON sfi.soa_cust_ft_hashkey = lsf.soa_cust_ft_hashkey
+),
+comg AS (
+    SELECT DISTINCT cg.mvalue AS branch_code, 1 AS is_com
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ocbh_co_group') cg
+    WHERE  cg.mvalue IS NOT NULL
+),
+hdtg AS (
+    SELECT hdi.account_no, tdi.user_created AS hdtg_user_created
+    FROM   sat_hdtg_dn hdi
+           LEFT JOIN sat_td_detail tdd ON tdd.hdtg_dn_id = hdi.serial_no
+           LEFT JOIN sat_td_info   tdi ON tdi.soa_cust_termdeposit_hashkey = tdd.soa_cust_termdeposit_hashkey
+),
+fxmm_noauto AS (
+    SELECT h.business_key AS fx_mm_id
+    FROM   forex_active h LEFT JOIN sat_fx_info i ON i.forex_hashkey = h.forex_hashkey
+    WHERE  i.t_deal_date &lt;&gt; i.t_value_date_buy OR i.t_deal_date &lt;&gt; i.t_value_date_sell
+    UNION
+    SELECT h.business_key
+    FROM   money_market_active h
+           LEFT JOIN sat_mm_info i ON i.money_market_hashkey = h.money_market_hashkey
+    WHERE  i.t_maturity_date = :DATADT
+),
+loans_br AS (
+    SELECT h.business_key AS contract_no, lb.branch_hashkey AS ar_ou_ip_id
+    FROM   loans_active h LEFT JOIN lnk_loans_branch lb ON lb.loans_hashkey = h.loans_hashkey
+),
+contract_ar AS (
+    SELECT business_key AS ref_no, deposit_hashkey           AS ar_hk, 'AZ' AS src FROM deposits_active
+    UNION ALL
+    SELECT business_key,            loans_hashkey,                     'LD' FROM loans_active
+    UNION ALL
+    SELECT business_key,            letter_of_credit_hashkey,          'TF' FROM letter_of_credit_active
+),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">line_mv_hub AS (
+    SELECT line_movement_toanhang_hashkey AS lm_hashkey,
+           t_line_id
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_line_movement_toanhang')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+line_mv AS (
+    SELECT lm_hashkey, t_line_id FROM line_mv_hub
+),
+gl_stmt_raw AS (
+    SELECT ll.stmt_entry_hashkey AS hk, lm.t_line_id, ll.source_event_date AS gl_dt
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_stmt_entry') ll
+           JOIN line_mv lm ON lm.lm_hashkey = ll.line_movement_toanhang_hashkey
+    WHERE  ll.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+gl_stmt AS (
+    SELECT hk, t_line_id, gl_dt FROM gl_stmt_raw
+),
+gl_categ_raw AS (
+    SELECT ll.categ_entry_hashkey AS hk, lm.t_line_id, ll.source_event_date AS gl_dt
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_categ_entry') ll
+           JOIN line_mv lm ON lm.lm_hashkey = ll.line_movement_toanhang_hashkey
+    WHERE  ll.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+gl_categ AS (
+    SELECT hk, t_line_id, gl_dt FROM gl_categ_raw
+),
+gl_recon_raw AS (
+    SELECT ll.re_consol_spec_entry_hashkey AS hk, lm.t_line_id, ll.source_event_date AS gl_dt
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_line_movement_toanhang_re_consol_spec_entry') ll
+           JOIN line_mv lm ON lm.lm_hashkey = ll.line_movement_toanhang_hashkey
+    WHERE  ll.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+gl_recon AS (
+    SELECT hk, t_line_id, gl_dt FROM gl_recon_raw
+),
+lnk_stmt_branch AS (
+    SELECT stmt_entry_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_stmt_entry_branch')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (stmt_entry_hashkey IN (SELECT hk FROM gl_stmt WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+    GROUP BY stmt_entry_hashkey
+),
+lnk_stmt_cust AS (
+    SELECT stmt_entry_hashkey,
+           max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_stmt_entry_customer')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (stmt_entry_hashkey IN (SELECT hk FROM gl_stmt WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+    GROUP BY stmt_entry_hashkey
+),
+lnk_categ_branch AS (
+    SELECT categ_entry_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_categ_entry_branch')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (categ_entry_hashkey IN (SELECT hk FROM gl_categ WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+    GROUP BY categ_entry_hashkey
+),
+lnk_categ_cust AS (
+    SELECT categ_entry_hashkey,
+           max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_categ_entry_customer')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (categ_entry_hashkey IN (SELECT hk FROM gl_categ WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+    GROUP BY categ_entry_hashkey
+),
+lnk_recon_branch AS (
+    SELECT re_consol_spec_entry_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_re_consol_spec_entry_branch')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (re_consol_spec_entry_hashkey IN (SELECT hk FROM gl_recon WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+    GROUP BY re_consol_spec_entry_hashkey
+),
+lnk_recon_cust AS (
+    SELECT re_consol_spec_entry_hashkey,
+           max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_re_consol_spec_entry_customer')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (re_consol_spec_entry_hashkey IN (SELECT hk FROM gl_recon WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+    GROUP BY re_consol_spec_entry_hashkey
+),
+stmt_info_raw AS (
+    SELECT i.stmt_entry_hashkey, i.source_event_date, i.t_amount_fcy, i.t_amount_lcy,
+           i.t_currency, i.t_trans_reference, i.t_narrative,
+           i.t_account_number, i.t_master_account
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_information') i
+    WHERE  i.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (i.stmt_entry_hashkey IN (SELECT hk FROM gl_stmt WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND i.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+),
+stmt_info AS (
+    SELECT stmt_entry_hashkey, source_event_date, t_amount_fcy, t_amount_lcy,
+           t_currency, t_trans_reference, t_narrative, t_account_number, t_master_account
+    FROM   stmt_info_raw
+),
+categ_info_raw AS (
+    SELECT i.categ_entry_hashkey, i.source_event_date, i.t_amount_fcy, i.t_amount_lcy,
+           i.t_currency, i.t_trans_reference, i.t_narrative
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_information') i
+    WHERE  i.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (i.categ_entry_hashkey IN (SELECT hk FROM gl_categ WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND i.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+),
+categ_info AS (
+    SELECT categ_entry_hashkey, source_event_date, t_amount_fcy, t_amount_lcy,
+           t_currency, t_trans_reference, t_narrative
+    FROM   categ_info_raw
+),
+recon_info_raw AS (
+    SELECT i.re_consol_spec_entry_hashkey, i.source_event_date, i.t_amount_fcy, i.t_amount_lcy,
+           i.t_currency, i.t_trans_reference, i.t_narrative, i.t_our_reference
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_re_consol_spec_entry_information') i
+    WHERE  i.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (i.re_consol_spec_entry_hashkey IN (SELECT hk FROM gl_recon WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND i.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+),
+recon_info AS (
+    SELECT re_consol_spec_entry_hashkey, source_event_date, t_amount_fcy, t_amount_lcy,
+           t_currency, t_trans_reference, t_narrative, t_our_reference
+    FROM   recon_info_raw
+),
+recon_cls_raw AS (
+    SELECT cl.re_consol_spec_entry_hashkey, cl.source_event_date,
+           cl.t_transaction_code, cl.t_product_category, cl.t_system_id
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_re_consol_spec_entry_classification') cl
+    WHERE  cl.source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+       OR  (cl.re_consol_spec_entry_hashkey IN (SELECT hk FROM gl_recon WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+            AND cl.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd'))
+),
+recon_cls AS (
+    SELECT re_consol_spec_entry_hashkey, source_event_date,
+           t_transaction_code, t_product_category, t_system_id
+    FROM   recon_cls_raw
+),
+drv_stmt AS (
+    SELECT hk FROM gl_stmt WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd')
+    UNION
+    SELECT stmt_entry_hashkey FROM stmt_info WHERE source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+drv_categ AS (
+    SELECT hk FROM gl_categ WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd')
+    UNION
+    SELECT categ_entry_hashkey FROM categ_info WHERE source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+drv_recon AS (
+    SELECT hk FROM gl_recon WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd')
+    UNION
+    SELECT re_consol_spec_entry_hashkey FROM recon_info
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+stmt_b AS (
+    SELECT h.stmt_entry_hashkey                                            AS PST_ENTR_ID,
+           CASE WHEN i.t_amount_fcy IS NULL AND i.t_currency = 'VND'
+                THEN i.t_amount_lcy ELSE i.t_amount_fcy END                AS AMT_FCY,
+           i.t_amount_lcy                                                  AS AMT_LCY,
+           i.t_currency                                                    AS CCY_ID,
+           lc.customer_hashkey                                             AS CST_ENTRY,
+           COALESCE(ham.ar_dw_id, ha.ar_dw_id)                             AS AR_ID,
+           CAST(SPLIT_PART(g.t_line_id,'-',2) AS INT)                      AS LINE_NBR,
+           regexp_replace(CAST(cl.t_transaction_code AS STRING),'\\.0+$','') AS TXN_TP_CODE,
+           cl.t_product_category                                           AS CGY_ID,
+           CASE WHEN a.t_record_status = 'REVE' THEN 105200003 ELSE 105200001 END AS PST_ENTR_ST_ID,
+           a.t_inputter, a.t_authoriser,
+           CAST(DATE_FORMAT(COALESCE(g.gl_dt, i.source_event_date),'yyyyMMdd') AS INT) AS CDR_DT_ID,
+           hb.business_key                                                 AS OU_ID,
+           lb.branch_hashkey                                               AS OU_DW_ID,
+           i.t_trans_reference, i.t_narrative,
+           i.t_account_number                                              AS ACCT_NO,
+           SPLIT_PART(g.t_line_id,'-',2)                                   AS GL,
+           SUBSTR(g.t_line_id, 20, 8)                                      AS GL_CDR_DT_ID,
+           'A'                                                             AS ENTRY_TYPE,
+           SPLIT_PART(i.t_trans_reference,'\\\\',1)                          AS TXN_KEY,
+           SUBSTR(i.t_trans_reference,1,12)                                AS FXMM_KEY,
+           CASE WHEN INSTR(i.t_trans_reference,'LD') &gt; 0
+                THEN SUBSTR(i.t_trans_reference, INSTR(i.t_trans_reference,'LD'), 12)
+                ELSE i.t_trans_reference END                               AS TXN_NO
+    FROM   drv_stmt dv
+           JOIN      stmt_info i  ON i.stmt_entry_hashkey  = dv.hk
+           LEFT JOIN (SELECT DISTINCT stmt_entry_hashkey FROM IDENTIFIER(:cleaned || '.raw_vault.hub_stmt_entry')
+                      WHERE source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+                         OR (stmt_entry_hashkey IN (SELECT hk FROM gl_stmt WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+                             AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')))                h  ON h.stmt_entry_hashkey  = i.stmt_entry_hashkey
+           LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_classification') cl ON cl.stmt_entry_hashkey = i.stmt_entry_hashkey
+                                                     AND cl.source_event_date = i.source_event_date
+                 AND cl.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+           LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_audit')          a  ON a.stmt_entry_hashkey  = i.stmt_entry_hashkey
+                                                     AND a.source_event_date  = i.source_event_date
+                 AND a.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+           LEFT JOIN lnk_stmt_branch lb ON lb.stmt_entry_hashkey = i.stmt_entry_hashkey
+           LEFT JOIN branch_active                    hb ON hb.branch_hashkey     = lb.branch_hashkey
+           LEFT JOIN lnk_stmt_cust   lc ON lc.stmt_entry_hashkey = i.stmt_entry_hashkey
+           LEFT JOIN account_active                   ha ON ha.business_key       = i.t_account_number
+           LEFT JOIN account_active                   ham ON ham.business_key      = i.t_master_account
+           LEFT JOIN gl_stmt                       g  ON g.hk                  = i.stmt_entry_hashkey
+    WHERE  COALESCE(g.gl_dt, i.source_event_date) = TO_DATE(:DATADT,'yyyyMMdd')
+),
+categ_b AS (
+    SELECT h2.categ_entry_hashkey                                          AS PST_ENTR_ID,
+           CASE WHEN i2.t_amount_fcy IS NULL AND i2.t_currency = 'VND'
+                THEN i2.t_amount_lcy ELSE i2.t_amount_fcy END              AS AMT_FCY,
+           i2.t_amount_lcy                                                 AS AMT_LCY,
+           i2.t_currency                                                   AS CCY_ID,
+           lc2.customer_hashkey                                            AS CST_ENTRY,
+           sha2(
+               CONCAT_WS('$',
+                   COALESCE(UPPER(TRIM(CAST(cl2.t_pl_category AS STRING))), ''),
+                   COALESCE(UPPER(TRIM(hb2.business_key)), ''),
+                   COALESCE(UPPER(TRIM(i2.t_currency)), '')
+               ), 256
+           )                                                               AS AR_ID,
+           CAST(SPLIT_PART(g.t_line_id,'-',2) AS INT)                      AS LINE_NBR,
+           regexp_replace(CAST(cl2.t_transaction_code AS STRING),'\\.0+$','') AS TXN_TP_CODE,
+           cl2.t_product_category                                          AS CGY_ID,
+           CAST(NULL AS INT)                                               AS PST_ENTR_ST_ID,
+           a2.t_inputter, a2.t_authoriser,
+           CAST(DATE_FORMAT(COALESCE(g.gl_dt, i2.source_event_date),'yyyyMMdd') AS INT) AS CDR_DT_ID,
+           hb2.business_key                                                AS OU_ID,
+           lb2.branch_hashkey                                              AS OU_DW_ID,
+           i2.t_trans_reference, i2.t_narrative,
+           CAST(NULL AS STRING)                                            AS ACCT_NO,
+           SPLIT_PART(g.t_line_id,'-',2)                                   AS GL,
+           SUBSTR(g.t_line_id, 20, 8)                                      AS GL_CDR_DT_ID,
+           'P'                                                             AS ENTRY_TYPE,
+           SPLIT_PART(i2.t_trans_reference,'\\\\',1)                         AS TXN_KEY,
+           SUBSTR(i2.t_trans_reference,1,12)                               AS FXMM_KEY,
+           CASE WHEN INSTR(i2.t_trans_reference,'LD') &gt; 0
+                THEN SUBSTR(i2.t_trans_reference, INSTR(i2.t_trans_reference,'LD'), 12)
+                ELSE i2.t_trans_reference END                              AS TXN_NO
+    FROM   drv_categ dv
+           JOIN      categ_info i2  ON i2.categ_entry_hashkey  = dv.hk
+           LEFT JOIN (SELECT DISTINCT categ_entry_hashkey FROM IDENTIFIER(:cleaned || '.raw_vault.hub_categ_entry')
+                      WHERE source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+                         OR (categ_entry_hashkey IN (SELECT hk FROM gl_categ WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+                             AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')))                h2  ON h2.categ_entry_hashkey  = i2.categ_entry_hashkey
+           LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_classification') cl2 ON cl2.categ_entry_hashkey = i2.categ_entry_hashkey
+                                                       AND cl2.source_event_date   = i2.source_event_date
+                 AND cl2.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+           LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_audit')          a2  ON a2.categ_entry_hashkey  = i2.categ_entry_hashkey
+                                                       AND a2.source_event_date    = i2.source_event_date
+                 AND a2.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+           LEFT JOIN lnk_categ_branch lb2 ON lb2.categ_entry_hashkey = i2.categ_entry_hashkey
+           LEFT JOIN branch_active                     hb2 ON hb2.branch_hashkey      = lb2.branch_hashkey
+           LEFT JOIN lnk_categ_cust   lc2 ON lc2.categ_entry_hashkey = i2.categ_entry_hashkey
+           LEFT JOIN gl_categ                       g   ON g.hk                    = i2.categ_entry_hashkey
+    WHERE  COALESCE(g.gl_dt, i2.source_event_date) = TO_DATE(:DATADT,'yyyyMMdd')
+),
+recon_key AS (
+    SELECT i3.re_consol_spec_entry_hashkey AS hk,
+           CASE WHEN cl3.t_system_id = 'AC' AND LEFT(i3.t_our_reference,2) = 'AZ'
+                     THEN SUBSTR(i3.t_our_reference,4,16)
+                WHEN cl3.t_system_id IN ('LD','PD')
+                     THEN SUBSTR(i3.t_our_reference, INSTR(i3.t_our_reference,'LD'), 12)
+                WHEN LEFT(i3.t_our_reference,2) = 'TF'
+                     THEN LEFT(i3.t_our_reference,12)
+                ELSE i3.t_our_reference END AS ref_no
+    FROM   recon_info i3
+           LEFT JOIN recon_cls cl3
+                  ON cl3.re_consol_spec_entry_hashkey = i3.re_consol_spec_entry_hashkey
+                 AND cl3.source_event_date           = i3.source_event_date
+                 AND cl3.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+),
+reconsol_b AS (
+    SELECT h3.re_consol_spec_entry_hashkey                                 AS PST_ENTR_ID,
+           CASE WHEN i3.t_amount_fcy IS NULL AND i3.t_currency = 'VND'
+                THEN i3.t_amount_lcy ELSE i3.t_amount_fcy END              AS AMT_FCY,
+           i3.t_amount_lcy                                                 AS AMT_LCY,
+           i3.t_currency                                                   AS CCY_ID,
+           lc3.customer_hashkey                                            AS CST_ENTRY,
+           car.ar_hk                                                       AS AR_ID,
+           CAST(SPLIT_PART(g.t_line_id,'-',2) AS INT)                      AS LINE_NBR,
+           regexp_replace(CAST(cl3.t_transaction_code AS STRING),'\\.0+$','') AS TXN_TP_CODE,
+           cl3.t_product_category                                          AS CGY_ID,
+           CASE WHEN a3.t_record_status = 'REVE' THEN 105200003 ELSE 105200001 END AS PST_ENTR_ST_ID,
+           a3.t_inputter, a3.t_authoriser,
+           CAST(DATE_FORMAT(COALESCE(g.gl_dt, i3.source_event_date),'yyyyMMdd') AS INT) AS CDR_DT_ID,
+           hb3.business_key                                                AS OU_ID,
+           lb3.branch_hashkey                                              AS OU_DW_ID,
+           i3.t_trans_reference, i3.t_narrative,
+           CAST(NULL AS STRING)                                            AS ACCT_NO,
+           SPLIT_PART(g.t_line_id,'-',2)                                   AS GL,
+           SUBSTR(g.t_line_id, 20, 8)                                      AS GL_CDR_DT_ID,
+           'R'                                                             AS ENTRY_TYPE,
+           SPLIT_PART(i3.t_trans_reference,'\\\\',1)                         AS TXN_KEY,
+           SUBSTR(i3.t_trans_reference,1,12)                               AS FXMM_KEY,
+           CASE WHEN INSTR(i3.t_trans_reference,'LD') &gt; 0
+                THEN SUBSTR(i3.t_trans_reference, INSTR(i3.t_trans_reference,'LD'), 12)
+                ELSE i3.t_trans_reference END                              AS TXN_NO
+    FROM   drv_recon dv
+           JOIN      recon_info i3
+                  ON i3.re_consol_spec_entry_hashkey = dv.hk
+           LEFT JOIN (SELECT DISTINCT re_consol_spec_entry_hashkey FROM IDENTIFIER(:cleaned || '.raw_vault.hub_re_consol_spec_entry')
+                      WHERE source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+                         OR (re_consol_spec_entry_hashkey IN (SELECT hk FROM gl_recon WHERE gl_dt = TO_DATE(:DATADT,'yyyyMMdd'))
+                             AND source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')))                h3
+                  ON h3.re_consol_spec_entry_hashkey = i3.re_consol_spec_entry_hashkey
+           LEFT JOIN recon_cls cl3
+                  ON cl3.re_consol_spec_entry_hashkey = i3.re_consol_spec_entry_hashkey
+                 AND cl3.source_event_date           = i3.source_event_date
+                 AND cl3.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+           LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_re_consol_spec_entry_audit')          a3
+                  ON a3.re_consol_spec_entry_hashkey  = i3.re_consol_spec_entry_hashkey
+                 AND a3.source_event_date            = i3.source_event_date
+                 AND a3.source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+           LEFT JOIN lnk_recon_branch lb3
+                  ON lb3.re_consol_spec_entry_hashkey = i3.re_consol_spec_entry_hashkey
+           LEFT JOIN branch_active                              hb3 ON hb3.branch_hashkey = lb3.branch_hashkey
+           LEFT JOIN lnk_recon_cust   lc3
+                  ON lc3.re_consol_spec_entry_hashkey = i3.re_consol_spec_entry_hashkey
+           LEFT JOIN gl_recon                                g   ON g.hk = i3.re_consol_spec_entry_hashkey
+           LEFT JOIN recon_key                               rk  ON rk.hk = i3.re_consol_spec_entry_hashkey
+           LEFT JOIN contract_ar                             car ON car.ref_no = rk.ref_no
+    WHERE  COALESCE(g.gl_dt, i3.source_event_date) = TO_DATE(:DATADT,'yyyyMMdd')
+),
+base AS (
+    SELECT PST_ENTR_ID, AMT_FCY, AMT_LCY, CCY_ID, CST_ENTRY, AR_ID, LINE_NBR, TXN_TP_CODE, CGY_ID,
+           PST_ENTR_ST_ID, t_inputter, t_authoriser, CDR_DT_ID, OU_ID, OU_DW_ID, t_trans_reference,
+           t_narrative, ACCT_NO, GL, GL_CDR_DT_ID, ENTRY_TYPE, TXN_KEY, FXMM_KEY, TXN_NO
+    FROM   stmt_b
+    UNION ALL
+    SELECT PST_ENTR_ID, AMT_FCY, AMT_LCY, CCY_ID, CST_ENTRY, AR_ID, LINE_NBR, TXN_TP_CODE, CGY_ID,
+           PST_ENTR_ST_ID, t_inputter, t_authoriser, CDR_DT_ID, OU_ID, OU_DW_ID, t_trans_reference,
+           t_narrative, ACCT_NO, GL, GL_CDR_DT_ID, ENTRY_TYPE, TXN_KEY, FXMM_KEY, TXN_NO
+    FROM   categ_b
+    UNION ALL
+    SELECT PST_ENTR_ID, AMT_FCY, AMT_LCY, CCY_ID, CST_ENTRY, AR_ID, LINE_NBR, TXN_TP_CODE, CGY_ID,
+           PST_ENTR_ST_ID, t_inputter, t_authoriser, CDR_DT_ID, OU_ID, OU_DW_ID, t_trans_reference,
+           t_narrative, ACCT_NO, GL, GL_CDR_DT_ID, ENTRY_TYPE, TXN_KEY, FXMM_KEY, TXN_NO
+    FROM   reconsol_b
+),
+enr AS (
+    SELECT b.PST_ENTR_ID, b.AMT_FCY, b.AMT_LCY, b.CCY_ID, b.CST_ENTRY, b.AR_ID, b.LINE_NBR,
+           b.TXN_TP_CODE, b.CGY_ID, b.PST_ENTR_ST_ID, b.t_inputter, b.t_authoriser, b.CDR_DT_ID,
+           b.OU_ID, b.OU_DW_ID, b.t_trans_reference, b.t_narrative, b.ACCT_NO, b.GL, b.GL_CDR_DT_ID,
+           b.ENTRY_TYPE, b.TXN_KEY, b.FXMM_KEY, b.TXN_NO,
+           t.dvc_id, t.txn_aprv, t.txn_ou_ip_id, t.txn_cst, t.ft_hashkey,
+           ch.channel_code,
+           CASE WHEN fx.fx_mm_id IS NOT NULL THEN 1 ELSE 0 END AS is_fx_mm_noauto,
+           lo.ar_ou_ip_id,
+           hd.hdtg_user_created
+    FROM   base b
+           LEFT JOIN txn         t  ON t.txn_ref      = b.TXN_KEY
+           LEFT JOIN chan        ch ON ch.ft_hashkey  = t.ft_hashkey
+           LEFT JOIN fxmm_noauto fx ON fx.fx_mm_id    = b.FXMM_KEY
+           LEFT JOIN loans_br    lo ON lo.contract_no = b.TXN_NO
+           LEFT JOIN hdtg        hd ON hd.account_no  = b.ACCT_NO
+),
+calc AS (
+    SELECT e.PST_ENTR_ID, e.AMT_FCY, e.AMT_LCY, e.CCY_ID, e.CST_ENTRY, e.AR_ID, e.LINE_NBR,
+           e.TXN_TP_CODE, e.CGY_ID, e.PST_ENTR_ST_ID, e.t_inputter, e.t_authoriser, e.CDR_DT_ID,
+           e.OU_ID, e.OU_DW_ID, e.t_trans_reference, e.t_narrative, e.ACCT_NO, e.GL, e.GL_CDR_DT_ID,
+           e.ENTRY_TYPE, e.TXN_KEY, e.FXMM_KEY, e.TXN_NO, e.dvc_id, e.txn_aprv, e.txn_ou_ip_id,
+           e.txn_cst, e.ft_hashkey, e.channel_code, e.is_fx_mm_noauto, e.ar_ou_ip_id,
+           e.hdtg_user_created,
+           CASE WHEN e.hdtg_user_created IS NOT NULL THEN e.hdtg_user_created
+                WHEN LEFT(e.dvc_id,1) = 'T'          THEN e.dvc_id
+                ELSE COALESCE(NULLIF(SPLIT_PART(e.t_inputter,'_',2),''), e.t_inputter) END AS INPUTER_ID,
+           CASE WHEN LEFT(e.dvc_id,1) = 'T'          THEN e.txn_aprv
+                ELSE COALESCE(NULLIF(SPLIT_PART(e.t_authoriser,'_',2),''), e.t_authoriser) END AS APRV_ID,
+           COALESCE(e.txn_cst, e.CST_ENTRY)                                        AS CST_ID,
+           CASE WHEN LEFT(e.TXN_NO,2) IN ('FT','TT') THEN COALESCE(e.txn_ou_ip_id, e.OU_DW_ID)
+                WHEN LEFT(e.TXN_NO,2) = 'LD'         THEN COALESCE(e.ar_ou_ip_id, e.OU_DW_ID)
+                ELSE e.OU_DW_ID END                                                AS OU_DW_ID_COM
+    FROM   enr e
+),
+fin AS (
+    SELECT c.PST_ENTR_ID, c.AMT_FCY, c.AMT_LCY, c.CCY_ID, c.CST_ENTRY, c.AR_ID, c.LINE_NBR,
+           c.TXN_TP_CODE, c.CGY_ID, c.PST_ENTR_ST_ID, c.t_inputter, c.t_authoriser, c.CDR_DT_ID,
+           c.OU_ID, c.OU_DW_ID, c.t_trans_reference, c.t_narrative, c.ACCT_NO, c.GL, c.GL_CDR_DT_ID,
+           c.ENTRY_TYPE, c.TXN_KEY, c.FXMM_KEY, c.TXN_NO, c.dvc_id, c.txn_aprv, c.txn_ou_ip_id,
+           c.txn_cst, c.ft_hashkey, c.channel_code, c.is_fx_mm_noauto, c.ar_ou_ip_id,
+           c.hdtg_user_created, c.INPUTER_ID, c.APRV_ID, c.CST_ID, c.OU_DW_ID_COM,
+           ui.user_hashkey AS INPTR_DW_ID, ui.auto_user, ui.user_com, ui.t_comp_report,
+           ua.user_hashkey AS APRV_DW_ID,
+           CASE WHEN cg.is_com = 1 THEN 1 ELSE 0 END AS is_com,
+           CASE WHEN c.TXN_TP_CODE IN ('182','183')                                          THEN 1
+                WHEN c.TXN_TP_CODE = '381' AND SUBSTR(CAST(c.LINE_NBR AS STRING),1,2) &lt;&gt; '10' THEN 1
+                WHEN c.TXN_TP_CODE IN ('366','367','494')
+                     AND c.t_narrative NOT LIKE 'EARLY REDEMPTION%'
+                     AND c.t_narrative NOT LIKE 'PRE CLOSURE%'                               THEN 1
+                WHEN c.ENTRY_TYPE = 'P'
+                     AND LEFT(c.t_trans_reference,2) NOT IN ('TT','FT','LD','PD','TF','DC','FX','MM','MD') THEN 1
+                WHEN LEFT(c.t_trans_reference,2) &lt;&gt; 'TF' AND c.ENTRY_TYPE = 'R'
+                     AND (LEFT(c.INPUTER_ID,1) &lt;&gt; 'T'
+                          OR (LEFT(c.INPUTER_ID,1) = 'T'
+                              AND LEFT(c.GL,1) NOT IN ('2','7') AND LEFT(c.GL,2) &lt;&gt; '92'
+                              AND LEFT(c.GL,3) NOT IN ('394','941','994','996')))            THEN 1
+                WHEN LEFT(c.t_trans_reference,2) = 'TF' AND c.GL = '9995'                     THEN 1
+                ELSE 0 END                                                          AS auto_src
+    FROM   calc c
+           LEFT JOIN usr  ui ON ui.usr_id = c.INPUTER_ID
+           LEFT JOIN usr  ua ON ua.usr_id = c.APRV_ID
+           LEFT JOIN comg cg ON cg.branch_code = c.OU_ID
+),
+flg AS (
+    SELECT f.PST_ENTR_ID, f.AMT_FCY, f.AMT_LCY, f.CCY_ID, f.CST_ENTRY, f.AR_ID, f.LINE_NBR,
+           f.TXN_TP_CODE, f.CGY_ID, f.PST_ENTR_ST_ID, f.t_inputter, f.t_authoriser, f.CDR_DT_ID,
+           f.OU_ID, f.OU_DW_ID, f.t_trans_reference, f.t_narrative, f.ACCT_NO, f.GL, f.GL_CDR_DT_ID,
+           f.ENTRY_TYPE, f.TXN_KEY, f.FXMM_KEY, f.TXN_NO, f.dvc_id, f.txn_aprv, f.txn_ou_ip_id,
+           f.txn_cst, f.ft_hashkey, f.channel_code, f.is_fx_mm_noauto, f.ar_ou_ip_id,
+           f.hdtg_user_created, f.INPUTER_ID, f.APRV_ID, f.CST_ID, f.OU_DW_ID_COM, f.INPTR_DW_ID,
+           f.auto_user, f.user_com, f.t_comp_report, f.APRV_DW_ID, f.is_com, f.auto_src,
+           CASE WHEN f.is_fx_mm_noauto = 1                                     THEN 0
+                WHEN f.channel_code IS NOT NULL AND f.channel_code &lt;&gt; 'BRANCH' THEN 1
+                WHEN f.auto_src = 0 AND LEFT(f.GL,3) IN ('994','996')          THEN 0
+                WHEN COALESCE(f.auto_user,0) = 1                               THEN 1
+                ELSE f.auto_src END                                             AS AUTO_DIM_ID
+    FROM   fin f
+)
+SELECT
+    g.PST_ENTR_ID, g.AMT_FCY, g.AMT_LCY,
+    CAST(1 AS SMALLINT)                                          AS NBR_OF_ITM,
+    g.CCY_ID, g.CST_ID, g.AR_ID, g.LINE_NBR,
+    g.TXN_TP_CODE                                                AS TXN_TP_ID,
+    COALESCE(CAST(g.CGY_ID AS INT), 0)                           AS CGY_ID,
+    g.PST_ENTR_ST_ID, g.INPUTER_ID, g.APRV_ID, g.CDR_DT_ID, g.OU_ID, g.OU_DW_ID,
+    CASE WHEN (COALESCE(g.user_com,0) = 1
+               OR (g.is_com = 1 AND LEFT(g.INPUTER_ID,3) = 'COB'))
+              AND g.AUTO_DIM_ID = 0 THEN NULL ELSE g.INPTR_DW_ID END        AS INPTR_DW_ID,
+    g.APRV_DW_ID,
+    CASE WHEN (COALESCE(g.user_com,0) = 1
+               OR (g.is_com = 1 AND LEFT(g.INPUTER_ID,3) = 'COB'))
+              AND g.AUTO_DIM_ID = 0 THEN NULL
+         WHEN LEFT(g.t_trans_reference,2) NOT IN ('FT','TT','DC','FX','AZ','TF','MM','PD','LD','SC')
+              AND LEFT(g.t_trans_reference,17) &lt;&gt; 'ONLINE.AC.CLOSURE'       THEN g.OU_DW_ID
+         WHEN hbu.branch_hashkey IS NOT NULL THEN
+              CASE WHEN LEFT(g.t_trans_reference,2) = 'LD'                  THEN hbu.branch_hashkey
+                   WHEN COALESCE(g.auto_user,0) = 1                         THEN g.OU_DW_ID
+                   ELSE hbu.branch_hashkey END
+         WHEN g.txn_ou_ip_id IS NOT NULL                                    THEN g.txn_ou_ip_id
+         ELSE g.OU_DW_ID END                                                AS OU_ID_CREATED,
+    g.AUTO_DIM_ID,
+    current_timestamp()                                          AS CRT_TM,
+    current_timestamp()                                          AS PPN_TM,
+    g.GL_CDR_DT_ID,
+    CASE WHEN (COALESCE(g.user_com,0) = 1
+               OR (g.is_com = 1 AND LEFT(g.INPUTER_ID,3) = 'COB'))
+              AND g.AUTO_DIM_ID = 0 THEN g.INPTR_DW_ID
+         ELSE NULL END                                              AS INPTR_DW_ID_COM,
+    CASE WHEN (COALESCE(g.user_com,0) = 1
+               OR (g.is_com = 1 AND LEFT(g.INPUTER_ID,3) = 'COB'))
+              AND g.AUTO_DIM_ID = 0 THEN g.OU_DW_ID_COM
+         ELSE NULL END                                              AS OU_ID_CREATED_COM
+FROM   flg g
+       LEFT JOIN branch_active hbu ON hbu.business_key = g.t_comp_report;
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">JOIN SCHEMA </t>
   </si>
   <si>
@@ -243,7 +1450,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +1543,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Consolas"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -408,7 +1623,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -620,11 +1835,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -687,6 +1913,33 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -705,23 +1958,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
@@ -1107,50 +2346,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="30" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="6" customHeight="1"/>
     <row r="3" spans="1:27" ht="8.25" customHeight="1"/>
     <row r="4" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A5" s="35"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="32"/>
+      <c r="C5" s="30"/>
     </row>
     <row r="6" spans="1:27" ht="8.25" customHeight="1">
-      <c r="A6" s="35"/>
+      <c r="A6" s="32"/>
     </row>
     <row r="7" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A7" s="35"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="30" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A8" s="36"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="32"/>
+      <c r="C8" s="30"/>
     </row>
     <row r="9" spans="1:27" ht="8.25" customHeight="1"/>
     <row r="10" spans="1:27" ht="21.75" customHeight="1"/>
@@ -1230,16 +2469,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="26" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1261,13 +2500,43 @@
       <c r="B3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15"/>
-    <row r="5" spans="1:4" ht="15"/>
-    <row r="6" spans="1:4" ht="15"/>
+    <row r="4" spans="1:4" ht="15">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.6">
+      <c r="A5" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15">
+      <c r="A6" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="7" spans="1:4" ht="15"/>
     <row r="8" spans="1:4" ht="15"/>
     <row r="9" spans="1:4" ht="15"/>
@@ -1293,47 +2562,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="A2" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="12" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="29"/>
+        <v>33</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="1:7" ht="64.5" customHeight="1">
       <c r="A4" s="22">
@@ -1343,68 +2612,68 @@
         <v>3</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="31"/>
+        <v>37</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="40"/>
     </row>
     <row r="5" spans="1:7" ht="55.5" customHeight="1">
       <c r="A5" s="23">
         <v>2</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
+        <v>42</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="40"/>
     </row>
     <row r="6" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="A6" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
     </row>
     <row r="7" spans="1:7" ht="14.45" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1415,19 +2684,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1438,19 +2707,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1461,19 +2730,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>45</v>
-      </c>
       <c r="E10" s="14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1484,19 +2753,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1507,19 +2776,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>45</v>
-      </c>
       <c r="E12" s="14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1530,19 +2799,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1553,19 +2822,19 @@
         <v>1</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7"/>
